--- a/testAffichageML/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/testAffichageML/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="122">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T09:34:46+00:00</t>
+    <t>2026-05-18T13:21:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -356,53 +356,19 @@
     <t>fr-lm-exposure-information.subSection</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-section
-</t>
-  </si>
-  <si>
     <t>Sous-sections</t>
   </si>
   <si>
     <t>fr-lm-section.subSection</t>
   </si>
   <si>
-    <t>fr-lm-exposure-information.subSection.codeSection</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.titleSection</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.description</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.author[x]</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.informant</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.subSection</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.subSection.entry</t>
+    <t>fr-lm-exposure-information.entry</t>
   </si>
   <si>
     <t>Entrées</t>
   </si>
   <si>
     <t>fr-lm-section.entry</t>
-  </si>
-  <si>
-    <t>fr-lm-exposure-information.entry</t>
   </si>
   <si>
     <t>fr-lm-exposure-information.subSection.quantityExposure</t>
@@ -724,7 +690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.57421875" customWidth="true" bestFit="true"/>
@@ -1802,13 +1768,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1859,7 +1825,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1876,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1887,10 +1853,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1902,13 +1868,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1959,13 +1925,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -1976,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1990,7 +1956,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2002,13 +1968,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2059,13 +2025,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2076,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2087,7 +2053,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>
@@ -2102,13 +2068,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2159,10 +2125,10 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>79</v>
@@ -2171,1006 +2137,6 @@
         <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q22" s="2"/>
-      <c r="R22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
         <v>73</v>
       </c>
     </row>
